--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484620_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484620_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.193</v>
+        <v>6.4667</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7182</v>
+        <v>2.5617</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4748</v>
+        <v>3.905</v>
       </c>
       <c r="G2" t="n">
         <v>2.8973</v>
@@ -610,13 +610,13 @@
         <v>3.6651</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4685</v>
+        <v>0.7423</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5792</v>
+        <v>0.4227</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8893</v>
+        <v>0.3195</v>
       </c>
       <c r="V2" t="n">
         <v>1.9109</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0922</v>
+        <v>2.8976</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2291</v>
+        <v>0.8611</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8631</v>
+        <v>2.0365</v>
       </c>
       <c r="G3" t="n">
         <v>4.3876</v>
@@ -688,13 +688,13 @@
         <v>3.2986</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2954</v>
+        <v>-0.49</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0098</v>
+        <v>-0.3778</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2856</v>
+        <v>-0.1122</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6335</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4086</v>
+        <v>1.6039</v>
       </c>
       <c r="E4" t="n">
-        <v>1.08</v>
+        <v>1.1761</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3287</v>
+        <v>0.4277</v>
       </c>
       <c r="G4" t="n">
         <v>1.691</v>
@@ -766,13 +766,13 @@
         <v>0.1833</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4656</v>
+        <v>-0.2704</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1903</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0658</v>
+        <v>0.9012</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2388</v>
+        <v>0.9503</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1729</v>
+        <v>-0.0491</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7015</v>
@@ -844,13 +844,13 @@
         <v>2.1991</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4317</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0015</v>
+        <v>-0.29</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4302</v>
+        <v>-0.3064</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5776</v>
+        <v>0.7595</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8037</v>
+        <v>-0.8448</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3813</v>
+        <v>1.6042</v>
       </c>
       <c r="G6" t="n">
         <v>-2.3637</v>
@@ -922,13 +922,13 @@
         <v>3.1154</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1479</v>
+        <v>0.3298</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5475</v>
+        <v>0.5064</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3996</v>
+        <v>-0.1767</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6533</v>
+        <v>0.6139</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6093</v>
+        <v>2.5297</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2626</v>
+        <v>-1.9158</v>
       </c>
       <c r="G7" t="n">
         <v>1.933</v>
@@ -1000,13 +1000,13 @@
         <v>2.5656</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1074</v>
+        <v>0.1599</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0467</v>
+        <v>-0.1263</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0607</v>
+        <v>0.2862</v>
       </c>
       <c r="V7" t="n">
         <v>-2.212</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9507</v>
+        <v>-0.8297</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7845</v>
+        <v>-0.6884</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1661</v>
+        <v>-0.1414</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3233</v>
@@ -1078,13 +1078,13 @@
         <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5333</v>
+        <v>-0.4123</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1652</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3681</v>
+        <v>-0.3433</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6439</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4864</v>
+        <v>-2.2227</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5407</v>
+        <v>-1.2523</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9456</v>
+        <v>-0.9704</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3786</v>
@@ -1156,13 +1156,13 @@
         <v>0.1833</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1078</v>
+        <v>0.1559</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1101</v>
+        <v>0.1784</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0023</v>
+        <v>-0.0224</v>
       </c>
       <c r="V9" t="n">
         <v>-1.267</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7187</v>
+        <v>-2.7279</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7453</v>
+        <v>-4.2095</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0266</v>
+        <v>1.4816</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4671</v>
@@ -1234,13 +1234,13 @@
         <v>2.5656</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5082</v>
+        <v>-0.5173</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3401</v>
+        <v>-0.8043</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8319</v>
+        <v>0.2869</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6439</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1669</v>
+        <v>-2.9716</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0708</v>
+        <v>-3.9746</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9039</v>
+        <v>1.003</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5467</v>
@@ -1312,13 +1312,13 @@
         <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0291</v>
+        <v>0.2244</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2738</v>
+        <v>0.3699</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2447</v>
+        <v>-0.1456</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5701</v>
+        <v>-3.4244</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3415</v>
+        <v>-0.2453</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2287</v>
+        <v>-3.1791</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1967</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5725</v>
+        <v>-0.4268</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4774</v>
+        <v>-0.3812</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0456</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5339</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7910999999999984</v>
+        <v>1.0665</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4111</v>
+        <v>-3.136</v>
       </c>
       <c r="F13" t="n">
-        <v>4.202500000000001</v>
+        <v>4.2022</v>
       </c>
       <c r="G13" t="n">
         <v>3.9313</v>
@@ -1468,13 +1468,13 @@
         <v>21.0746</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3764</v>
+        <v>-1.1008</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0256</v>
+        <v>-0.7503</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3509000000000002</v>
+        <v>-0.3509</v>
       </c>
       <c r="V13" t="n">
         <v>-6.3452</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.103</v>
+        <v>4.9931</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8536</v>
+        <v>3.3344</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2493</v>
+        <v>1.6587</v>
       </c>
       <c r="G14" t="n">
         <v>3.9658</v>
@@ -1546,13 +1546,13 @@
         <v>3.1154</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4043</v>
+        <v>0.4859</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.589</v>
+        <v>-0.1082</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1847</v>
+        <v>0.594</v>
       </c>
       <c r="V14" t="n">
         <v>4.7563</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8408</v>
+        <v>2.7258</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6574</v>
+        <v>1.3689</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1835</v>
+        <v>1.3569</v>
       </c>
       <c r="G15" t="n">
         <v>1.9929</v>
@@ -1624,13 +1624,13 @@
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4349</v>
+        <v>-0.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0905</v>
+        <v>-0.198</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5254</v>
+        <v>-0.352</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.247</v>
+        <v>2.3342</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8766</v>
+        <v>1.832</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3704</v>
+        <v>0.5021</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2957</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5267</v>
+        <v>0.4584</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.231</v>
+        <v>0.3626</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2976</v>
+        <v>1.5051</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4706</v>
+        <v>0.6936</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1729</v>
+        <v>0.8115</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.002</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0561</v>
+        <v>-0.2351</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0581</v>
+        <v>-0.4489</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
         <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5353</v>
+        <v>0.2015</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4457</v>
+        <v>-0.0237</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0896</v>
+        <v>0.2253</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9658</v>
+        <v>0.945</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9658</v>
+        <v>1.267</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7936</v>
+        <v>1.5594</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5436</v>
+        <v>0.0112</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2501</v>
+        <v>1.5482</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.2957</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4584</v>
+        <v>2.5267</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3626</v>
+        <v>-2.231</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5051</v>
+        <v>0.2976</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6936</v>
+        <v>1.4706</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8115</v>
+        <v>-1.1729</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.002</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2351</v>
+        <v>1.0561</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4489</v>
+        <v>-1.0581</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3665</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
         <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.339</v>
+        <v>0.8477</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3122</v>
+        <v>0.5803</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0268</v>
+        <v>0.2673</v>
       </c>
       <c r="V17" t="n">
-        <v>0.945</v>
+        <v>0.9658</v>
       </c>
       <c r="W17" t="n">
-        <v>1.267</v>
+        <v>0.9658</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6495</v>
+        <v>1.3611</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2002</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0.4493</v>
@@ -1858,10 +1858,10 @@
         <v>0.3665</v>
       </c>
       <c r="S18" t="n">
-        <v>0.678</v>
+        <v>0.3895</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5309</v>
+        <v>0.2425</v>
       </c>
       <c r="U18" t="n">
         <v>0.1471</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.009</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.4136</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.5954</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.7002</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.6198</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.0805</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.0527</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.4059</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.4586</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.7529</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.2139</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.5391</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.1595</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.8823</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3418</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0672</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.409</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7002</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6198</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0805</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0527</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4059</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4586</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7529</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2139</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5391</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4923</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2036</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.005</v>
+        <v>-0.3009</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1588</v>
+        <v>-0.5434</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1638</v>
+        <v>0.2424</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8232</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4617</v>
+        <v>0.1557</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2006</v>
+        <v>-0.184</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2611</v>
+        <v>0.3397</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0813</v>
+        <v>-0.7651</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7762</v>
+        <v>-0.5839</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3051</v>
+        <v>-0.1812</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7973</v>
@@ -2170,13 +2170,13 @@
         <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6505</v>
+        <v>-0.3343</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4302</v>
+        <v>-0.3064</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1518</v>
+        <v>-2.9304</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5209</v>
+        <v>-1.3286</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6309</v>
+        <v>-1.6018</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8452</v>
@@ -2248,13 +2248,13 @@
         <v>0.3665</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0842</v>
+        <v>0.1373</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3673</v>
+        <v>-0.175</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2831</v>
+        <v>0.3122</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5889</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2241</v>
+        <v>-4.7899</v>
       </c>
       <c r="E24" t="n">
         <v>-5.9026</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6784</v>
+        <v>1.1126</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5347</v>
@@ -2326,13 +2326,13 @@
         <v>2.9321</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1982</v>
+        <v>0.6323</v>
       </c>
       <c r="T24" t="n">
         <v>-0.003</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2012</v>
+        <v>0.6353</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2903</v>
+        <v>-5.0397</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8834</v>
+        <v>-4.6911</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4068</v>
+        <v>-0.3486</v>
       </c>
       <c r="G25" t="n">
         <v>-4.6196</v>
@@ -2404,13 +2404,13 @@
         <v>1.8326</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.1742</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2217</v>
+        <v>-0.0294</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1454</v>
+        <v>0.2036</v>
       </c>
       <c r="V25" t="n">
         <v>0.3219</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.791500000000001</v>
+        <v>1.131899999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-4.202399999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>3.411</v>
+        <v>5.334000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-3.9313</v>
@@ -2482,13 +2482,13 @@
         <v>16.4932</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3763</v>
+        <v>3.2993</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3507000000000001</v>
+        <v>0.3508000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>1.0257</v>
+        <v>2.948399999999999</v>
       </c>
       <c r="V26" t="n">
         <v>6.345200000000001</v>
